--- a/Iron_Vengeance_Tracker_Template.xlsx
+++ b/Iron_Vengeance_Tracker_Template.xlsx
@@ -1147,7 +1147,7 @@
       </c>
       <c r="B11" s="6" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>528589132.750632</v>
+        <v>574363156.896709</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
